--- a/data/uretim_verileri.xlsx
+++ b/data/uretim_verileri.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="6" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="6" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kaynak Referans" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,16 +73,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -171,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -234,6 +245,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -601,13 +622,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="18.6640625" customWidth="1" style="21" min="1" max="1"/>
-    <col width="12.109375" customWidth="1" style="21" min="2" max="2"/>
-    <col width="15.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.44140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" style="21" min="1" max="1"/>
+    <col width="18" customWidth="1" style="21" min="2" max="2"/>
+    <col width="18" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+    <col width="18" bestFit="1" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -616,9 +637,19 @@
           <t>Kodlar</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Cycle time</t>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Kaynak Süresi (sn)</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Söktak Süresi (sn)</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Toplam Cycle (sn)</t>
         </is>
       </c>
     </row>
@@ -629,7 +660,14 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2">
+        <f>B2+C2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -639,7 +677,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>17.14285714285714</v>
+        <v>6.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D3">
+        <f>B3+C3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -649,7 +694,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4">
+        <f>B4+C4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -659,7 +711,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D5">
+        <f>B5+C5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -669,7 +728,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <f>B6+C6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -679,7 +745,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C7" t="n">
+        <v>144</v>
+      </c>
+      <c r="D7">
+        <f>B7+C7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -689,7 +762,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C8" t="n">
+        <v>144</v>
+      </c>
+      <c r="D8">
+        <f>B8+C8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -699,7 +779,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>28.8</v>
+        <v>11.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D9">
+        <f>B9+C9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -709,7 +796,14 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C10" t="n">
+        <v>54</v>
+      </c>
+      <c r="D10">
+        <f>B10+C10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -719,7 +813,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>257.1428571428572</v>
+        <v>102.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="D11">
+        <f>B11+C11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -729,7 +830,14 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>42.35294117647059</v>
+        <v>16.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D12">
+        <f>B12+C12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -739,7 +847,14 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>48</v>
+        <v>19.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D13">
+        <f>B13+C13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -749,7 +864,14 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>72</v>
+      </c>
+      <c r="D14">
+        <f>B14+C14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -759,7 +881,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C15" t="n">
+        <v>54</v>
+      </c>
+      <c r="D15">
+        <f>B15+C15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -769,7 +898,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>54</v>
+      </c>
+      <c r="D16">
+        <f>B16+C16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -779,7 +915,14 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>360</v>
+        <v>144</v>
+      </c>
+      <c r="C17" t="n">
+        <v>216</v>
+      </c>
+      <c r="D17">
+        <f>B17+C17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -789,7 +932,14 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <f>B18+C18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -799,7 +949,14 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C19" t="n">
+        <v>54</v>
+      </c>
+      <c r="D19">
+        <f>B19+C19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -809,7 +966,14 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C20" t="n">
+        <v>36</v>
+      </c>
+      <c r="D20">
+        <f>B20+C20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -819,7 +983,14 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C21" t="n">
+        <v>108</v>
+      </c>
+      <c r="D21">
+        <f>B21+C21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -829,7 +1000,14 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>153.0000114750009</v>
+        <v>61.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D22">
+        <f>B22+C22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -839,7 +1017,14 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C23" t="n">
+        <v>72</v>
+      </c>
+      <c r="D23">
+        <f>B23+C23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -849,7 +1034,14 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C24" t="n">
+        <v>36</v>
+      </c>
+      <c r="D24">
+        <f>B24+C24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -859,7 +1051,14 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D25">
+        <f>B25+C25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -869,7 +1068,14 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C26" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26">
+        <f>B26+C26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -879,7 +1085,14 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D27">
+        <f>B27+C27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -889,7 +1102,14 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D28">
+        <f>B28+C28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -899,7 +1119,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C29" t="n">
+        <v>108</v>
+      </c>
+      <c r="D29">
+        <f>B29+C29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -909,7 +1136,14 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D30">
+        <f>B30+C30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -919,7 +1153,14 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C31" t="n">
+        <v>270</v>
+      </c>
+      <c r="D31">
+        <f>B31+C31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -929,7 +1170,14 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C32" t="n">
+        <v>270</v>
+      </c>
+      <c r="D32">
+        <f>B32+C32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -939,7 +1187,14 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>305.9998929000375</v>
+        <v>122.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D33">
+        <f>B33+C33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -949,7 +1204,14 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D34">
+        <f>B34+C34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -959,7 +1221,14 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>305.0847457627119</v>
+        <v>122</v>
+      </c>
+      <c r="C35" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="D35">
+        <f>B35+C35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -969,7 +1238,14 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36">
+        <f>B36+C36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -979,7 +1255,14 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C37" t="n">
+        <v>108</v>
+      </c>
+      <c r="D37">
+        <f>B37+C37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -989,7 +1272,14 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <f>B38+C38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -999,7 +1289,14 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D39">
+        <f>B39+C39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1009,7 +1306,14 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>225</v>
+        <v>90</v>
+      </c>
+      <c r="C40" t="n">
+        <v>135</v>
+      </c>
+      <c r="D40">
+        <f>B40+C40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1019,7 +1323,14 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D41">
+        <f>B41+C41</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1029,7 +1340,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D42">
+        <f>B42+C42</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1039,7 +1357,14 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>48</v>
+        <v>19.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D43">
+        <f>B43+C43</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -1049,7 +1374,14 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>92.30769230769231</v>
+        <v>36.9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="D44">
+        <f>B44+C44</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -1059,7 +1391,14 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>225</v>
+        <v>90</v>
+      </c>
+      <c r="C45" t="n">
+        <v>135</v>
+      </c>
+      <c r="D45">
+        <f>B45+C45</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1069,7 +1408,14 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C46" t="n">
+        <v>270</v>
+      </c>
+      <c r="D46">
+        <f>B46+C46</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1079,7 +1425,14 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>257.1428571428572</v>
+        <v>102.9</v>
+      </c>
+      <c r="C47" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="D47">
+        <f>B47+C47</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1089,7 +1442,14 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>23.07692307692308</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D48">
+        <f>B48+C48</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1099,7 +1459,14 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>72</v>
+      </c>
+      <c r="D49">
+        <f>B49+C49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -1109,7 +1476,14 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C50" t="n">
+        <v>54</v>
+      </c>
+      <c r="D50">
+        <f>B50+C50</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1119,7 +1493,14 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C51" t="n">
+        <v>72</v>
+      </c>
+      <c r="D51">
+        <f>B51+C51</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1129,7 +1510,14 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C52" t="n">
+        <v>36</v>
+      </c>
+      <c r="D52">
+        <f>B52+C52</f>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1139,7 +1527,14 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C53" t="n">
+        <v>108</v>
+      </c>
+      <c r="D53">
+        <f>B53+C53</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -1149,7 +1544,14 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>257.1428571428572</v>
+        <v>102.9</v>
+      </c>
+      <c r="C54" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="D54">
+        <f>B54+C54</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -1159,7 +1561,14 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C55" t="n">
+        <v>54</v>
+      </c>
+      <c r="D55">
+        <f>B55+C55</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1169,7 +1578,14 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D56">
+        <f>B56+C56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1179,7 +1595,14 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D57">
+        <f>B57+C57</f>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -1189,7 +1612,14 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C58" t="n">
+        <v>108</v>
+      </c>
+      <c r="D58">
+        <f>B58+C58</f>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1199,7 +1629,14 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C59" t="n">
+        <v>36</v>
+      </c>
+      <c r="D59">
+        <f>B59+C59</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1646,14 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C60" t="n">
+        <v>108</v>
+      </c>
+      <c r="D60">
+        <f>B60+C60</f>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -1219,7 +1663,14 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C61" t="n">
+        <v>108</v>
+      </c>
+      <c r="D61">
+        <f>B61+C61</f>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -1229,7 +1680,14 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D62">
+        <f>B62+C62</f>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -1239,7 +1697,14 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D63">
+        <f>B63+C63</f>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -1249,7 +1714,14 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C64" t="n">
+        <v>72</v>
+      </c>
+      <c r="D64">
+        <f>B64+C64</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -1259,7 +1731,14 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>24</v>
+      </c>
+      <c r="D65">
+        <f>B65+C65</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -1269,7 +1748,14 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C66" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D66">
+        <f>B66+C66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -1279,7 +1765,14 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D67">
+        <f>B67+C67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -1289,7 +1782,14 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C68" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D68">
+        <f>B68+C68</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -1299,7 +1799,14 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C69" t="n">
+        <v>120</v>
+      </c>
+      <c r="D69">
+        <f>B69+C69</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -1309,7 +1816,14 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>54.54545454545455</v>
+        <v>21.8</v>
+      </c>
+      <c r="C70" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="D70">
+        <f>B70+C70</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -1319,7 +1833,14 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C71" t="n">
+        <v>72</v>
+      </c>
+      <c r="D71">
+        <f>B71+C71</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -1329,7 +1850,14 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C72" t="n">
+        <v>270</v>
+      </c>
+      <c r="D72">
+        <f>B72+C72</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -1339,7 +1867,14 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C73" t="n">
+        <v>144</v>
+      </c>
+      <c r="D73">
+        <f>B73+C73</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -1349,7 +1884,14 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C74" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D74">
+        <f>B74+C74</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -1359,7 +1901,14 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C75" t="n">
+        <v>270</v>
+      </c>
+      <c r="D75">
+        <f>B75+C75</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -1369,7 +1918,14 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C76" t="n">
+        <v>108</v>
+      </c>
+      <c r="D76">
+        <f>B76+C76</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -1379,7 +1935,14 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>78.26086956521739</v>
+        <v>31.3</v>
+      </c>
+      <c r="C77" t="n">
+        <v>47</v>
+      </c>
+      <c r="D77">
+        <f>B77+C77</f>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -1389,7 +1952,14 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C78" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D78">
+        <f>B78+C78</f>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -1399,7 +1969,14 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C79" t="n">
+        <v>120</v>
+      </c>
+      <c r="D79">
+        <f>B79+C79</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -1409,7 +1986,14 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C80" t="n">
+        <v>18</v>
+      </c>
+      <c r="D80">
+        <f>B80+C80</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -1419,7 +2003,14 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C81" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D81">
+        <f>B81+C81</f>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -1429,7 +2020,14 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>76.59574468085107</v>
+        <v>30.6</v>
+      </c>
+      <c r="C82" t="n">
+        <v>46</v>
+      </c>
+      <c r="D82">
+        <f>B82+C82</f>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -1439,7 +2037,14 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>305.9998929000375</v>
+        <v>122.4</v>
+      </c>
+      <c r="C83" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D83">
+        <f>B83+C83</f>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -1449,7 +2054,14 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>218.5714051530637</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="D84">
+        <f>B84+C84</f>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -1459,7 +2071,14 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>174.857102889805</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="D85">
+        <f>B85+C85</f>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -1469,7 +2088,14 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>327.2727272727273</v>
+        <v>130.9</v>
+      </c>
+      <c r="C86" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="D86">
+        <f>B86+C86</f>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -1479,7 +2105,14 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>48</v>
+        <v>19.2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D87">
+        <f>B87+C87</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -1489,7 +2122,14 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>24</v>
+      </c>
+      <c r="D88">
+        <f>B88+C88</f>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -1499,7 +2139,14 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>24</v>
+      </c>
+      <c r="D89">
+        <f>B89+C89</f>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -1509,7 +2156,14 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C90" t="n">
+        <v>72</v>
+      </c>
+      <c r="D90">
+        <f>B90+C90</f>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -1519,7 +2173,14 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D91">
+        <f>B91+C91</f>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -1529,7 +2190,14 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>218.5714051530637</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="D92">
+        <f>B92+C92</f>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -1539,7 +2207,14 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+      <c r="D93">
+        <f>B93+C93</f>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -1549,7 +2224,14 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C94" t="n">
+        <v>144</v>
+      </c>
+      <c r="D94">
+        <f>B94+C94</f>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -1559,7 +2241,14 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D95">
+        <f>B95+C95</f>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -1569,7 +2258,14 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>163.6363636363636</v>
+        <v>65.5</v>
+      </c>
+      <c r="C96" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="D96">
+        <f>B96+C96</f>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -1579,7 +2275,14 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>30.59998929000375</v>
+        <v>12.2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D97">
+        <f>B97+C97</f>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -1589,7 +2292,14 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C98" t="n">
+        <v>18</v>
+      </c>
+      <c r="D98">
+        <f>B98+C98</f>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -1599,7 +2309,14 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>36</v>
+        <v>14.4</v>
+      </c>
+      <c r="C99" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D99">
+        <f>B99+C99</f>
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -1609,7 +2326,14 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>36</v>
+        <v>14.4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D100">
+        <f>B100+C100</f>
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -1619,7 +2343,14 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C101" t="n">
+        <v>27</v>
+      </c>
+      <c r="D101">
+        <f>B101+C101</f>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -1629,7 +2360,14 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C102" t="n">
+        <v>54</v>
+      </c>
+      <c r="D102">
+        <f>B102+C102</f>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -1639,7 +2377,14 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C103" t="n">
+        <v>54</v>
+      </c>
+      <c r="D103">
+        <f>B103+C103</f>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -1649,7 +2394,14 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C104" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D104">
+        <f>B104+C104</f>
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -1659,7 +2411,14 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>85.71428571428571</v>
+        <v>34.3</v>
+      </c>
+      <c r="C105" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D105">
+        <f>B105+C105</f>
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -1669,7 +2428,14 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>300</v>
+        <v>120</v>
+      </c>
+      <c r="C106" t="n">
+        <v>180</v>
+      </c>
+      <c r="D106">
+        <f>B106+C106</f>
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -1679,7 +2445,14 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C107" t="n">
+        <v>54</v>
+      </c>
+      <c r="D107">
+        <f>B107+C107</f>
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -1689,7 +2462,14 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C108" t="n">
+        <v>36</v>
+      </c>
+      <c r="D108">
+        <f>B108+C108</f>
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -1699,7 +2479,14 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C109" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D109">
+        <f>B109+C109</f>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -1709,7 +2496,14 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>171.4285714285714</v>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="C110" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="D110">
+        <f>B110+C110</f>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -1719,7 +2513,14 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C111" t="n">
+        <v>54</v>
+      </c>
+      <c r="D111">
+        <f>B111+C111</f>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -1729,7 +2530,14 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C112" t="n">
+        <v>54</v>
+      </c>
+      <c r="D112">
+        <f>B112+C112</f>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -1739,7 +2547,14 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C113" t="n">
+        <v>72</v>
+      </c>
+      <c r="D113">
+        <f>B113+C113</f>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -1749,7 +2564,14 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>75</v>
+        <v>30</v>
+      </c>
+      <c r="C114" t="n">
+        <v>45</v>
+      </c>
+      <c r="D114">
+        <f>B114+C114</f>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -1759,7 +2581,14 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C115" t="n">
+        <v>18</v>
+      </c>
+      <c r="D115">
+        <f>B115+C115</f>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -1769,7 +2598,14 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>24</v>
+      </c>
+      <c r="D116">
+        <f>B116+C116</f>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -1779,7 +2615,14 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C117" t="n">
+        <v>72</v>
+      </c>
+      <c r="D117">
+        <f>B117+C117</f>
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -1789,7 +2632,14 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C118" t="n">
+        <v>54</v>
+      </c>
+      <c r="D118">
+        <f>B118+C118</f>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -1799,7 +2649,14 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>450</v>
+        <v>180</v>
+      </c>
+      <c r="C119" t="n">
+        <v>270</v>
+      </c>
+      <c r="D119">
+        <f>B119+C119</f>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -1809,7 +2666,14 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C120" t="n">
+        <v>18</v>
+      </c>
+      <c r="D120">
+        <f>B120+C120</f>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -1819,7 +2683,14 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C121" t="n">
+        <v>54</v>
+      </c>
+      <c r="D121">
+        <f>B121+C121</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -1829,7 +2700,14 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C122" t="n">
+        <v>54</v>
+      </c>
+      <c r="D122">
+        <f>B122+C122</f>
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -1839,7 +2717,14 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C123" t="n">
+        <v>54</v>
+      </c>
+      <c r="D123">
+        <f>B123+C123</f>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -1849,7 +2734,14 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>360</v>
+        <v>144</v>
+      </c>
+      <c r="C124" t="n">
+        <v>216</v>
+      </c>
+      <c r="D124">
+        <f>B124+C124</f>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -1859,7 +2751,14 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>73.46938775510205</v>
+        <v>29.4</v>
+      </c>
+      <c r="C125" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D125">
+        <f>B125+C125</f>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -1869,7 +2768,14 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C126" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D126">
+        <f>B126+C126</f>
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -1879,7 +2785,14 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>257.1428571428572</v>
+        <v>102.9</v>
+      </c>
+      <c r="C127" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="D127">
+        <f>B127+C127</f>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -1889,7 +2802,14 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="C128" t="n">
+        <v>18</v>
+      </c>
+      <c r="D128">
+        <f>B128+C128</f>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -1899,7 +2819,14 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>300</v>
+        <v>120</v>
+      </c>
+      <c r="C129" t="n">
+        <v>180</v>
+      </c>
+      <c r="D129">
+        <f>B129+C129</f>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -1909,7 +2836,14 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C130" t="n">
+        <v>54</v>
+      </c>
+      <c r="D130">
+        <f>B130+C130</f>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -1919,7 +2853,14 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C131" t="n">
+        <v>72</v>
+      </c>
+      <c r="D131">
+        <f>B131+C131</f>
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -1929,7 +2870,14 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>133.3333333333333</v>
+        <v>53.3</v>
+      </c>
+      <c r="C132" t="n">
+        <v>80</v>
+      </c>
+      <c r="D132">
+        <f>B132+C132</f>
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -1939,7 +2887,14 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>34.28571428571428</v>
+        <v>13.7</v>
+      </c>
+      <c r="C133" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D133">
+        <f>B133+C133</f>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -1949,7 +2904,14 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C134" t="n">
+        <v>108</v>
+      </c>
+      <c r="D134">
+        <f>B134+C134</f>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -1959,7 +2921,14 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C135" t="n">
+        <v>108</v>
+      </c>
+      <c r="D135">
+        <f>B135+C135</f>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -1969,7 +2938,14 @@
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>156.5217391304348</v>
+        <v>62.6</v>
+      </c>
+      <c r="C136" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D136">
+        <f>B136+C136</f>
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -1979,7 +2955,14 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>112.5</v>
+        <v>45</v>
+      </c>
+      <c r="C137" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="D137">
+        <f>B137+C137</f>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -1989,7 +2972,14 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>203.9999864000009</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="C138" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="D138">
+        <f>B138+C138</f>
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -1999,7 +2989,14 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C139" t="n">
+        <v>36</v>
+      </c>
+      <c r="D139">
+        <f>B139+C139</f>
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -2009,7 +3006,14 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>53.73134328358209</v>
+        <v>21.5</v>
+      </c>
+      <c r="C140" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D140">
+        <f>B140+C140</f>
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -2019,7 +3023,14 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>276.9230769230769</v>
+        <v>110.8</v>
+      </c>
+      <c r="C141" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="D141">
+        <f>B141+C141</f>
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -2029,7 +3040,14 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>87.80487804878049</v>
+        <v>35.1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="D142">
+        <f>B142+C142</f>
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -2039,7 +3057,14 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D143">
+        <f>B143+C143</f>
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -2049,7 +3074,14 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C144" t="n">
+        <v>12</v>
+      </c>
+      <c r="D144">
+        <f>B144+C144</f>
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -2059,7 +3091,14 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>42.85714285714285</v>
+        <v>17.1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D145">
+        <f>B145+C145</f>
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -2069,7 +3108,14 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C146" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D146">
+        <f>B146+C146</f>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -2079,7 +3125,14 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C147" t="n">
+        <v>144</v>
+      </c>
+      <c r="D147">
+        <f>B147+C147</f>
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -2089,7 +3142,14 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C148" t="n">
+        <v>108</v>
+      </c>
+      <c r="D148">
+        <f>B148+C148</f>
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -2099,7 +3159,14 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C149" t="n">
+        <v>120</v>
+      </c>
+      <c r="D149">
+        <f>B149+C149</f>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -2109,7 +3176,14 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C150" t="n">
+        <v>36</v>
+      </c>
+      <c r="D150">
+        <f>B150+C150</f>
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -2119,7 +3193,14 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>51.42857142857143</v>
+        <v>20.6</v>
+      </c>
+      <c r="C151" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D151">
+        <f>B151+C151</f>
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -2129,7 +3210,14 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C152" t="n">
+        <v>36</v>
+      </c>
+      <c r="D152">
+        <f>B152+C152</f>
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -2139,7 +3227,14 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C153" t="n">
+        <v>144</v>
+      </c>
+      <c r="D153">
+        <f>B153+C153</f>
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -2149,7 +3244,14 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C154" t="n">
+        <v>27</v>
+      </c>
+      <c r="D154">
+        <f>B154+C154</f>
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -2159,7 +3261,14 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>300</v>
+        <v>120</v>
+      </c>
+      <c r="C155" t="n">
+        <v>180</v>
+      </c>
+      <c r="D155">
+        <f>B155+C155</f>
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -2169,7 +3278,14 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C156" t="n">
+        <v>36</v>
+      </c>
+      <c r="D156">
+        <f>B156+C156</f>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -2179,7 +3295,14 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C157" t="n">
+        <v>27</v>
+      </c>
+      <c r="D157">
+        <f>B157+C157</f>
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -2189,7 +3312,14 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C158" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D158">
+        <f>B158+C158</f>
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -2199,7 +3329,14 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C159" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D159">
+        <f>B159+C159</f>
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -2209,7 +3346,14 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C160" t="n">
+        <v>72</v>
+      </c>
+      <c r="D160">
+        <f>B160+C160</f>
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -2219,7 +3363,14 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C161" t="n">
+        <v>72</v>
+      </c>
+      <c r="D161">
+        <f>B161+C161</f>
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -2229,7 +3380,14 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C162" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D162">
+        <f>B162+C162</f>
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -2239,7 +3397,14 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C163" t="n">
+        <v>36</v>
+      </c>
+      <c r="D163">
+        <f>B163+C163</f>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -2249,7 +3414,14 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>300</v>
+        <v>120</v>
+      </c>
+      <c r="C164" t="n">
+        <v>180</v>
+      </c>
+      <c r="D164">
+        <f>B164+C164</f>
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -2259,7 +3431,14 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>360</v>
+        <v>144</v>
+      </c>
+      <c r="C165" t="n">
+        <v>216</v>
+      </c>
+      <c r="D165">
+        <f>B165+C165</f>
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -2269,7 +3448,14 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C166" t="n">
+        <v>54</v>
+      </c>
+      <c r="D166">
+        <f>B166+C166</f>
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -2279,7 +3465,14 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C167" t="n">
+        <v>72</v>
+      </c>
+      <c r="D167">
+        <f>B167+C167</f>
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -2289,7 +3482,14 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>65.45454545454545</v>
+        <v>26.2</v>
+      </c>
+      <c r="C168" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="D168">
+        <f>B168+C168</f>
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -2299,7 +3499,14 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D169">
+        <f>B169+C169</f>
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -2309,7 +3516,14 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>34.28571428571428</v>
+        <v>13.7</v>
+      </c>
+      <c r="C170" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D170">
+        <f>B170+C170</f>
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -2319,7 +3533,14 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C171" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D171">
+        <f>B171+C171</f>
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -2329,7 +3550,14 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C172" t="n">
+        <v>54</v>
+      </c>
+      <c r="D172">
+        <f>B172+C172</f>
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -2339,7 +3567,14 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>24</v>
+      </c>
+      <c r="D173">
+        <f>B173+C173</f>
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -2349,7 +3584,14 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D174">
+        <f>B174+C174</f>
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -2359,7 +3601,14 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C175" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D175">
+        <f>B175+C175</f>
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -2369,7 +3618,14 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>144</v>
+        <v>57.6</v>
+      </c>
+      <c r="C176" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D176">
+        <f>B176+C176</f>
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -2379,7 +3635,14 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D177">
+        <f>B177+C177</f>
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +3652,14 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C178" t="n">
+        <v>54</v>
+      </c>
+      <c r="D178">
+        <f>B178+C178</f>
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -2399,7 +3669,14 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>51.42857142857143</v>
+        <v>20.6</v>
+      </c>
+      <c r="C179" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D179">
+        <f>B179+C179</f>
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -2409,7 +3686,14 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C180" t="n">
+        <v>54</v>
+      </c>
+      <c r="D180">
+        <f>B180+C180</f>
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -2419,7 +3703,14 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D181">
+        <f>B181+C181</f>
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -2429,7 +3720,14 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C182" t="n">
+        <v>54</v>
+      </c>
+      <c r="D182">
+        <f>B182+C182</f>
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -2439,7 +3737,14 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C183" t="n">
+        <v>72</v>
+      </c>
+      <c r="D183">
+        <f>B183+C183</f>
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -2449,7 +3754,14 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="C184" t="n">
+        <v>144</v>
+      </c>
+      <c r="D184">
+        <f>B184+C184</f>
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -2459,7 +3771,14 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C185" t="n">
+        <v>108</v>
+      </c>
+      <c r="D185">
+        <f>B185+C185</f>
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -2469,7 +3788,14 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>102.8571428571429</v>
+        <v>41.1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D186">
+        <f>B186+C186</f>
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -2479,7 +3805,14 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>72</v>
+        <v>28.8</v>
+      </c>
+      <c r="C187" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D187">
+        <f>B187+C187</f>
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -2489,7 +3822,14 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="C188" t="n">
+        <v>72</v>
+      </c>
+      <c r="D188">
+        <f>B188+C188</f>
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -2499,7 +3839,14 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C189" t="n">
+        <v>108</v>
+      </c>
+      <c r="D189">
+        <f>B189+C189</f>
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -2509,7 +3856,14 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C190" t="n">
+        <v>108</v>
+      </c>
+      <c r="D190">
+        <f>B190+C190</f>
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -2519,7 +3873,14 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C191" t="n">
+        <v>48</v>
+      </c>
+      <c r="D191">
+        <f>B191+C191</f>
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -2529,7 +3890,14 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>400</v>
+        <v>160</v>
+      </c>
+      <c r="C192" t="n">
+        <v>240</v>
+      </c>
+      <c r="D192">
+        <f>B192+C192</f>
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -2539,7 +3907,14 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>160</v>
+        <v>64</v>
+      </c>
+      <c r="C193" t="n">
+        <v>96</v>
+      </c>
+      <c r="D193">
+        <f>B193+C193</f>
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -2549,7 +3924,14 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C194" t="n">
+        <v>108</v>
+      </c>
+      <c r="D194">
+        <f>B194+C194</f>
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -2559,7 +3941,14 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>730</v>
+        <v>292</v>
+      </c>
+      <c r="C195" t="n">
+        <v>438</v>
+      </c>
+      <c r="D195">
+        <f>B195+C195</f>
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -2569,7 +3958,14 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>730</v>
+        <v>292</v>
+      </c>
+      <c r="C196" t="n">
+        <v>438</v>
+      </c>
+      <c r="D196">
+        <f>B196+C196</f>
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -2579,7 +3975,14 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>730</v>
+        <v>292</v>
+      </c>
+      <c r="C197" t="n">
+        <v>438</v>
+      </c>
+      <c r="D197">
+        <f>B197+C197</f>
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -2589,7 +3992,14 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C198" t="n">
+        <v>108</v>
+      </c>
+      <c r="D198">
+        <f>B198+C198</f>
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -2599,7 +4009,14 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="C199" t="n">
+        <v>108</v>
+      </c>
+      <c r="D199">
+        <f>B199+C199</f>
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -2609,7 +4026,14 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C200" t="n">
+        <v>15</v>
+      </c>
+      <c r="D200">
+        <f>B200+C200</f>
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -2619,7 +4043,14 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C201" t="n">
+        <v>15</v>
+      </c>
+      <c r="D201">
+        <f>B201+C201</f>
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -2629,7 +4060,14 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>70</v>
+        <v>28</v>
+      </c>
+      <c r="C202" t="n">
+        <v>42</v>
+      </c>
+      <c r="D202">
+        <f>B202+C202</f>
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -2639,9 +4077,15 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C203" s="4" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D203">
+        <f>B203+C203</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -2650,10 +4094,15 @@
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C204" s="6" t="n"/>
-      <c r="D204" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D204" s="7">
+        <f>B204+C204</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -2662,10 +4111,15 @@
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C205" s="6" t="n"/>
-      <c r="D205" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D205" s="7">
+        <f>B205+C205</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -2674,10 +4128,15 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="C206" s="6" t="n"/>
-      <c r="D206" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D206" s="7">
+        <f>B206+C206</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -2686,10 +4145,15 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C207" s="6" t="n"/>
-      <c r="D207" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C207" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D207" s="7">
+        <f>B207+C207</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -2698,10 +4162,15 @@
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="C208" s="6" t="n"/>
-      <c r="D208" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="C208" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D208" s="7">
+        <f>B208+C208</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -2710,10 +4179,15 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C209" s="6" t="n"/>
-      <c r="D209" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D209" s="7">
+        <f>B209+C209</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -2722,10 +4196,15 @@
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="C210" s="6" t="n"/>
-      <c r="D210" s="7" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="C210" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="D210" s="7">
+        <f>B210+C210</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -2734,10 +4213,15 @@
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C211" s="6" t="n"/>
-      <c r="D211" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D211" s="7">
+        <f>B211+C211</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -2746,10 +4230,15 @@
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C212" s="6" t="n"/>
-      <c r="D212" s="7" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="C212" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D212" s="7">
+        <f>B212+C212</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -2758,10 +4247,15 @@
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="7" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="D213" s="7">
+        <f>B213+C213</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -2770,10 +4264,15 @@
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="C214" s="6" t="n"/>
-      <c r="D214" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C214" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D214" s="7">
+        <f>B214+C214</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -2782,10 +4281,15 @@
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C215" s="6" t="n"/>
-      <c r="D215" s="7" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="C215" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D215" s="7">
+        <f>B215+C215</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -2794,10 +4298,15 @@
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="C216" s="6" t="n"/>
-      <c r="D216" s="7" t="n"/>
+        <v>160</v>
+      </c>
+      <c r="C216" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="D216" s="7">
+        <f>B216+C216</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -2806,10 +4315,15 @@
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="C217" s="6" t="n"/>
-      <c r="D217" s="7" t="n"/>
+        <v>144</v>
+      </c>
+      <c r="C217" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="D217" s="7">
+        <f>B217+C217</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -2818,10 +4332,15 @@
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="C218" s="6" t="n"/>
-      <c r="D218" s="7" t="n"/>
+        <v>144</v>
+      </c>
+      <c r="C218" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="D218" s="7">
+        <f>B218+C218</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -2830,10 +4349,15 @@
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C219" s="6" t="n"/>
-      <c r="D219" s="7" t="n"/>
+        <v>14.4</v>
+      </c>
+      <c r="C219" s="6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D219" s="7">
+        <f>B219+C219</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -2842,10 +4366,15 @@
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="C220" s="6" t="n"/>
-      <c r="D220" s="7" t="n"/>
+        <v>144</v>
+      </c>
+      <c r="C220" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="D220" s="7">
+        <f>B220+C220</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -2854,9 +4383,15 @@
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C221" s="4" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="C221" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="D221">
+        <f>B221+C221</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="8" t="inlineStr">
@@ -2865,7 +4400,14 @@
         </is>
       </c>
       <c r="B222" s="8" t="n">
-        <v>70</v>
+        <v>28</v>
+      </c>
+      <c r="C222" t="n">
+        <v>42</v>
+      </c>
+      <c r="D222">
+        <f>B222+C222</f>
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -2875,7 +4417,14 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>95</v>
+        <v>38</v>
+      </c>
+      <c r="C223" t="n">
+        <v>57</v>
+      </c>
+      <c r="D223">
+        <f>B223+C223</f>
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -2885,7 +4434,14 @@
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C224" t="n">
+        <v>12</v>
+      </c>
+      <c r="D224">
+        <f>B224+C224</f>
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -2895,7 +4451,14 @@
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C225" t="n">
+        <v>12</v>
+      </c>
+      <c r="D225">
+        <f>B225+C225</f>
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -2905,7 +4468,14 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="C226" t="n">
+        <v>51</v>
+      </c>
+      <c r="D226">
+        <f>B226+C226</f>
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -2915,7 +4485,14 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="C227" t="n">
+        <v>51</v>
+      </c>
+      <c r="D227">
+        <f>B227+C227</f>
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -2925,7 +4502,14 @@
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>110</v>
+        <v>44</v>
+      </c>
+      <c r="C228" t="n">
+        <v>66</v>
+      </c>
+      <c r="D228">
+        <f>B228+C228</f>
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -2935,7 +4519,14 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="C229" t="n">
+        <v>30</v>
+      </c>
+      <c r="D229">
+        <f>B229+C229</f>
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -2945,7 +4536,14 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C230" t="n">
+        <v>15</v>
+      </c>
+      <c r="D230">
+        <f>B230+C230</f>
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -2955,7 +4553,14 @@
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C231" t="n">
+        <v>15</v>
+      </c>
+      <c r="D231">
+        <f>B231+C231</f>
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -2965,7 +4570,14 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C232" t="n">
+        <v>15</v>
+      </c>
+      <c r="D232">
+        <f>B232+C232</f>
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -2975,7 +4587,14 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C233" t="n">
+        <v>15</v>
+      </c>
+      <c r="D233">
+        <f>B233+C233</f>
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -2985,7 +4604,14 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C234" t="n">
+        <v>15</v>
+      </c>
+      <c r="D234">
+        <f>B234+C234</f>
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -2995,7 +4621,14 @@
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C235" t="n">
+        <v>15</v>
+      </c>
+      <c r="D235">
+        <f>B235+C235</f>
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -3005,7 +4638,14 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>150</v>
+        <v>60</v>
+      </c>
+      <c r="C236" t="n">
+        <v>90</v>
+      </c>
+      <c r="D236">
+        <f>B236+C236</f>
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -3015,7 +4655,14 @@
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C237" t="n">
+        <v>36</v>
+      </c>
+      <c r="D237">
+        <f>B237+C237</f>
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -3025,7 +4672,14 @@
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C238" t="n">
+        <v>54</v>
+      </c>
+      <c r="D238">
+        <f>B238+C238</f>
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -3035,7 +4689,14 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C239" t="n">
+        <v>27</v>
+      </c>
+      <c r="D239">
+        <f>B239+C239</f>
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -3045,7 +4706,14 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>75</v>
+        <v>30</v>
+      </c>
+      <c r="C240" t="n">
+        <v>45</v>
+      </c>
+      <c r="D240">
+        <f>B240+C240</f>
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -3055,7 +4723,14 @@
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>55</v>
+        <v>22</v>
+      </c>
+      <c r="C241" t="n">
+        <v>33</v>
+      </c>
+      <c r="D241">
+        <f>B241+C241</f>
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -3065,7 +4740,14 @@
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>130</v>
+        <v>80</v>
+      </c>
+      <c r="C242" t="n">
+        <v>120</v>
+      </c>
+      <c r="D242">
+        <f>B242+C242</f>
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -3075,7 +4757,14 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>182</v>
+        <v>72.8</v>
+      </c>
+      <c r="C243" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="D243">
+        <f>B243+C243</f>
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -3085,7 +4774,14 @@
         </is>
       </c>
       <c r="B244" s="11" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C244" t="n">
+        <v>54</v>
+      </c>
+      <c r="D244">
+        <f>B244+C244</f>
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -3095,7 +4791,14 @@
         </is>
       </c>
       <c r="B245" s="11" t="n">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="C245" t="n">
+        <v>54</v>
+      </c>
+      <c r="D245">
+        <f>B245+C245</f>
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -3105,7 +4808,14 @@
         </is>
       </c>
       <c r="B246" s="11" t="n">
-        <v>113</v>
+        <v>45.2</v>
+      </c>
+      <c r="C246" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="D246">
+        <f>B246+C246</f>
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -3115,7 +4825,14 @@
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="C247" t="n">
+        <v>51</v>
+      </c>
+      <c r="D247">
+        <f>B247+C247</f>
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -3125,7 +4842,14 @@
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>160</v>
+        <v>64</v>
+      </c>
+      <c r="C248" t="n">
+        <v>96</v>
+      </c>
+      <c r="D248">
+        <f>B248+C248</f>
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -3135,7 +4859,14 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>58</v>
+        <v>23.2</v>
+      </c>
+      <c r="C249" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D249">
+        <f>B249+C249</f>
+        <v/>
       </c>
     </row>
     <row r="250">
@@ -3145,7 +4876,14 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>778</v>
+        <v>311.2</v>
+      </c>
+      <c r="C250" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="D250">
+        <f>B250+C250</f>
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -3155,7 +4893,14 @@
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C251" t="n">
+        <v>48</v>
+      </c>
+      <c r="D251">
+        <f>B251+C251</f>
+        <v/>
       </c>
     </row>
     <row r="252">
@@ -3165,7 +4910,14 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C252" t="n">
+        <v>48</v>
+      </c>
+      <c r="D252">
+        <f>B252+C252</f>
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -3175,7 +4927,14 @@
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C253" t="n">
+        <v>36</v>
+      </c>
+      <c r="D253">
+        <f>B253+C253</f>
+        <v/>
       </c>
     </row>
     <row r="254">
@@ -3185,7 +4944,14 @@
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C254" t="n">
+        <v>48</v>
+      </c>
+      <c r="D254">
+        <f>B254+C254</f>
+        <v/>
       </c>
     </row>
     <row r="255">
@@ -3195,7 +4961,14 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C255" t="n">
+        <v>48</v>
+      </c>
+      <c r="D255">
+        <f>B255+C255</f>
+        <v/>
       </c>
     </row>
     <row r="256">
@@ -3205,7 +4978,14 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="C256" t="n">
+        <v>48</v>
+      </c>
+      <c r="D256">
+        <f>B256+C256</f>
+        <v/>
       </c>
     </row>
     <row r="257">
@@ -3215,10 +4995,15 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C257" s="15" t="n"/>
-      <c r="D257" s="16" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="C257" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="D257" s="16">
+        <f>B257+C257</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
@@ -3227,10 +5012,15 @@
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="C258" s="15" t="n"/>
-      <c r="D258" s="16" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C258" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="D258" s="16">
+        <f>B258+C258</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="17" t="inlineStr">
@@ -3239,10 +5029,15 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C259" s="15" t="n"/>
-      <c r="D259" s="16" t="n"/>
+        <v>19.2</v>
+      </c>
+      <c r="C259" s="15" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D259" s="16">
+        <f>B259+C259</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="17" t="inlineStr">
@@ -3251,10 +5046,15 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="C260" s="15" t="n"/>
-      <c r="D260" s="16" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="C260" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="D260" s="16">
+        <f>B260+C260</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -3263,10 +5063,15 @@
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="C261" s="15" t="n"/>
-      <c r="D261" s="16" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C261" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="D261" s="16">
+        <f>B261+C261</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -3275,10 +5080,15 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C262" s="15" t="n"/>
-      <c r="D262" s="16" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="C262" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="D262" s="16">
+        <f>B262+C262</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="17" t="inlineStr">
@@ -3287,10 +5097,15 @@
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C263" s="15" t="n"/>
-      <c r="D263" s="16" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="C263" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="D263" s="16">
+        <f>B263+C263</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="17" t="inlineStr">
@@ -3299,10 +5114,15 @@
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="C264" s="15" t="n"/>
-      <c r="D264" s="16" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="C264" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="D264" s="16">
+        <f>B264+C264</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="17" t="inlineStr">
@@ -3311,10 +5131,15 @@
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C265" s="15" t="n"/>
-      <c r="D265" s="16" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C265" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D265" s="16">
+        <f>B265+C265</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
@@ -3323,10 +5148,15 @@
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C266" s="15" t="n"/>
-      <c r="D266" s="16" t="n"/>
+        <v>19.2</v>
+      </c>
+      <c r="C266" s="15" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D266" s="16">
+        <f>B266+C266</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="17" t="inlineStr">
@@ -3335,10 +5165,317 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C267" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="D267" s="16">
+        <f>B267+C267</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>10.300.0609P</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>18</v>
+      </c>
+      <c r="C268" t="n">
+        <v>27</v>
+      </c>
+      <c r="D268">
+        <f>B268+C268</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>10.300.0776GW(HAZ)</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>20</v>
+      </c>
+      <c r="C269" t="n">
+        <v>30</v>
+      </c>
+      <c r="D269">
+        <f>B269+C269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>10.300.0776GW(Hazırlık)</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>28</v>
+      </c>
+      <c r="C270" t="n">
+        <v>42</v>
+      </c>
+      <c r="D270">
+        <f>B270+C270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>10.300.3840Hz</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>10.300.4726W</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>60</v>
+      </c>
+      <c r="C272" t="n">
         <v>90</v>
       </c>
-      <c r="C267" s="15" t="n"/>
-      <c r="D267" s="16" t="n"/>
+      <c r="D272">
+        <f>B272+C272</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>10.300.5117W</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>10.300.6415 1. Opr</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>40</v>
+      </c>
+      <c r="C274" t="n">
+        <v>60</v>
+      </c>
+      <c r="D274">
+        <f>B274+C274</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>10.300.6415 2. Opr</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>40</v>
+      </c>
+      <c r="C275" t="n">
+        <v>60</v>
+      </c>
+      <c r="D275">
+        <f>B275+C275</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>10.300.6415(SOMUN)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>30</v>
+      </c>
+      <c r="C276" t="n">
+        <v>45</v>
+      </c>
+      <c r="D276">
+        <f>B276+C276</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>10.300.6463W-10</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>40</v>
+      </c>
+      <c r="C277" t="n">
+        <v>60</v>
+      </c>
+      <c r="D277">
+        <f>B277+C277</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>94.LTK.341/10</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>240</v>
+      </c>
+      <c r="C278" t="n">
+        <v>360</v>
+      </c>
+      <c r="D278">
+        <f>B278+C278</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>94.LTK.455/10</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>240</v>
+      </c>
+      <c r="C279" t="n">
+        <v>360</v>
+      </c>
+      <c r="D279">
+        <f>B279+C279</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>94.ltk.733</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>REF-001</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>18</v>
+      </c>
+      <c r="C281" t="n">
+        <v>27</v>
+      </c>
+      <c r="D281">
+        <f>B281+C281</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>REF-002</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C282" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D282">
+        <f>B282+C282</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>REF-003</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C283" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D283">
+        <f>B283+C283</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>REF-004</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>24</v>
+      </c>
+      <c r="C284" t="n">
+        <v>36</v>
+      </c>
+      <c r="D284">
+        <f>B284+C284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>REF-005</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C285" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D285">
+        <f>B285+C285</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>10.300.0446.3 (Somun)</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>100</v>
+      </c>
+      <c r="C286" t="n">
+        <v>150</v>
+      </c>
+      <c r="D286">
+        <f>B286+C286</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3352,142 +5489,142 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R248"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ROBOT</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>RAFNO</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>ABB-1</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>ABB-2</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>ABB-3</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I1" s="24" t="inlineStr">
         <is>
           <t>ABB-4</t>
         </is>
       </c>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="K1" s="24" t="inlineStr">
         <is>
           <t>ABB-5</t>
         </is>
       </c>
-      <c r="M1" s="23" t="inlineStr">
+      <c r="M1" s="24" t="inlineStr">
         <is>
           <t>ABB-6</t>
         </is>
       </c>
-      <c r="O1" s="23" t="inlineStr">
+      <c r="O1" s="24" t="inlineStr">
         <is>
           <t>ABB-7</t>
         </is>
       </c>
-      <c r="Q1" s="23" t="inlineStr">
+      <c r="Q1" s="24" t="inlineStr">
         <is>
           <t>ABB-8</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>İSTASYON</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="J2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="L2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr">
+      <c r="M2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="N2" s="23" t="inlineStr">
+      <c r="N2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="O2" s="23" t="inlineStr">
+      <c r="O2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="P2" s="23" t="inlineStr">
+      <c r="P2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
       </c>
-      <c r="Q2" s="23" t="inlineStr">
+      <c r="Q2" s="24" t="inlineStr">
         <is>
           <t>İST-1</t>
         </is>
       </c>
-      <c r="R2" s="23" t="inlineStr">
+      <c r="R2" s="24" t="inlineStr">
         <is>
           <t>İST-2</t>
         </is>
@@ -12552,20 +14689,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H107"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>A RAFI</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>B RAFI</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>C RAFI</t>
         </is>
@@ -15075,7 +17212,7 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15188,8 +17325,8 @@
   <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="23.44140625" customWidth="1" min="1" max="1"/>
-    <col width="12.6640625" customWidth="1" min="3" max="3"/>
+    <col width="23.44140625" customWidth="1" style="25" min="1" max="1"/>
+    <col width="12.6640625" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18408,8 +20545,8 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" style="25" min="1" max="1"/>
+    <col width="18.6640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18550,7 +20687,7 @@
   <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="18.109375" customWidth="1" min="1" max="1"/>
+    <col width="18.109375" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19229,8 +21366,8 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="3.44140625" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="3.44140625" customWidth="1" style="25" min="1" max="1"/>
+    <col width="19" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19310,7 +21447,7 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="25.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.5546875" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19735,7 +21872,7 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="25.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.5546875" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20052,11 +22189,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="25.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="12.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="25.5546875" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12.44140625" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20292,12 +22429,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mekanik Arıza Durumu</t>
+          <t>Maden Takviyesi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plansız</t>
+          <t>Planlı</t>
         </is>
       </c>
     </row>
@@ -20307,7 +22444,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elektrik Arıza Durumu</t>
+          <t>Mekanik Arıza Durumu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -20322,7 +22459,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Malzeme Bekleme</t>
+          <t>Elektrik Arıza Durumu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -20337,7 +22474,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>İhtiyaç Molası</t>
+          <t>Malzeme Bekleme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -20352,7 +22489,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eksik Parça Durumu</t>
+          <t>İhtiyaç Molası</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -20367,10 +22504,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Eksik Parça Durumu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plansız</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Eksik Operatör Durumu</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Plansız</t>
         </is>

--- a/data/uretim_verileri.xlsx
+++ b/data/uretim_verileri.xlsx
@@ -726,7 +726,6 @@
         <f>B2+C2</f>
         <v/>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -744,7 +743,6 @@
         <f>B3+C3</f>
         <v/>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -784,7 +782,6 @@
         <f>B5+C5</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -802,7 +799,6 @@
         <f>B6+C6</f>
         <v/>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -820,7 +816,6 @@
         <f>B7+C7</f>
         <v/>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -838,7 +833,6 @@
         <f>B8+C8</f>
         <v/>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -856,7 +850,6 @@
         <f>B9+C9</f>
         <v/>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -874,7 +867,6 @@
         <f>B10+C10</f>
         <v/>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -892,7 +884,6 @@
         <f>B11+C11</f>
         <v/>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -910,7 +901,6 @@
         <f>B12+C12</f>
         <v/>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -994,7 +984,6 @@
         <f>B16+C16</f>
         <v/>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1012,7 +1001,6 @@
         <f>B17+C17</f>
         <v/>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1030,7 +1018,6 @@
         <f>B18+C18</f>
         <v/>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1048,7 +1035,6 @@
         <f>B19+C19</f>
         <v/>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1088,7 +1074,6 @@
         <f>B21+C21</f>
         <v/>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1106,7 +1091,6 @@
         <f>B22+C22</f>
         <v/>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1124,7 +1108,6 @@
         <f>B23+C23</f>
         <v/>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1142,7 +1125,6 @@
         <f>B24+C24</f>
         <v/>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1160,7 +1142,6 @@
         <f>B25+C25</f>
         <v/>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1178,7 +1159,6 @@
         <f>B26+C26</f>
         <v/>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1196,7 +1176,6 @@
         <f>B27+C27</f>
         <v/>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1214,7 +1193,6 @@
         <f>B28+C28</f>
         <v/>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1232,7 +1210,6 @@
         <f>B29+C29</f>
         <v/>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1250,7 +1227,6 @@
         <f>B30+C30</f>
         <v/>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
@@ -1268,7 +1244,6 @@
         <f>B31+C31</f>
         <v/>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
@@ -1286,7 +1261,6 @@
         <f>B32+C32</f>
         <v/>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
@@ -1304,7 +1278,6 @@
         <f>B33+C33</f>
         <v/>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1322,7 +1295,6 @@
         <f>B34+C34</f>
         <v/>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
@@ -1340,7 +1312,6 @@
         <f>B35+C35</f>
         <v/>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1358,7 +1329,6 @@
         <f>B36+C36</f>
         <v/>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1376,7 +1346,6 @@
         <f>B37+C37</f>
         <v/>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1394,7 +1363,6 @@
         <f>B38+C38</f>
         <v/>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1412,7 +1380,6 @@
         <f>B39+C39</f>
         <v/>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1430,7 +1397,6 @@
         <f>B40+C40</f>
         <v/>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1448,7 +1414,6 @@
         <f>B41+C41</f>
         <v/>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1466,7 +1431,6 @@
         <f>B42+C42</f>
         <v/>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1484,7 +1448,6 @@
         <f>B43+C43</f>
         <v/>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1502,7 +1465,6 @@
         <f>B44+C44</f>
         <v/>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1520,7 +1482,6 @@
         <f>B45+C45</f>
         <v/>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
@@ -1538,7 +1499,6 @@
         <f>B46+C46</f>
         <v/>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
@@ -1556,7 +1516,6 @@
         <f>B47+C47</f>
         <v/>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1574,7 +1533,6 @@
         <f>B48+C48</f>
         <v/>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1614,7 +1572,6 @@
         <f>B50+C50</f>
         <v/>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1632,7 +1589,6 @@
         <f>B51+C51</f>
         <v/>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1650,7 +1606,6 @@
         <f>B52+C52</f>
         <v/>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1668,7 +1623,6 @@
         <f>B53+C53</f>
         <v/>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
@@ -1686,7 +1640,6 @@
         <f>B54+C54</f>
         <v/>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1704,7 +1657,6 @@
         <f>B55+C55</f>
         <v/>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1722,7 +1674,6 @@
         <f>B56+C56</f>
         <v/>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1740,7 +1691,6 @@
         <f>B57+C57</f>
         <v/>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1758,7 +1708,6 @@
         <f>B58+C58</f>
         <v/>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1776,7 +1725,6 @@
         <f>B59+C59</f>
         <v/>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1794,7 +1742,6 @@
         <f>B60+C60</f>
         <v/>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1812,7 +1759,6 @@
         <f>B61+C61</f>
         <v/>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1830,7 +1776,6 @@
         <f>B62+C62</f>
         <v/>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1848,7 +1793,6 @@
         <f>B63+C63</f>
         <v/>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1866,7 +1810,6 @@
         <f>B64+C64</f>
         <v/>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1884,7 +1827,6 @@
         <f>B65+C65</f>
         <v/>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1924,7 +1866,6 @@
         <f>B67+C67</f>
         <v/>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1942,7 +1883,6 @@
         <f>B68+C68</f>
         <v/>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1960,7 +1900,6 @@
         <f>B69+C69</f>
         <v/>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1978,7 +1917,6 @@
         <f>B70+C70</f>
         <v/>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1996,7 +1934,6 @@
         <f>B71+C71</f>
         <v/>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
@@ -2014,7 +1951,6 @@
         <f>B72+C72</f>
         <v/>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
@@ -2032,7 +1968,6 @@
         <f>B73+C73</f>
         <v/>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
@@ -2094,7 +2029,6 @@
         <f>B76+C76</f>
         <v/>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2134,7 +2068,6 @@
         <f>B78+C78</f>
         <v/>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2152,7 +2085,6 @@
         <f>B79+C79</f>
         <v/>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2170,7 +2102,6 @@
         <f>B80+C80</f>
         <v/>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2210,7 +2141,6 @@
         <f>B82+C82</f>
         <v/>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
@@ -2316,7 +2246,6 @@
         <f>B87+C87</f>
         <v/>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2378,7 +2307,6 @@
         <f>B90+C90</f>
         <v/>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2418,7 +2346,6 @@
         <f>B92+C92</f>
         <v/>
       </c>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2458,7 +2385,6 @@
         <f>B94+C94</f>
         <v/>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2476,7 +2402,6 @@
         <f>B95+C95</f>
         <v/>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2494,7 +2419,6 @@
         <f>B96+C96</f>
         <v/>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2534,7 +2458,6 @@
         <f>B98+C98</f>
         <v/>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2552,7 +2475,6 @@
         <f>B99+C99</f>
         <v/>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2570,7 +2492,6 @@
         <f>B100+C100</f>
         <v/>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2588,7 +2509,6 @@
         <f>B101+C101</f>
         <v/>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2606,7 +2526,6 @@
         <f>B102+C102</f>
         <v/>
       </c>
-      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2624,7 +2543,6 @@
         <f>B103+C103</f>
         <v/>
       </c>
-      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2642,7 +2560,6 @@
         <f>B104+C104</f>
         <v/>
       </c>
-      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2682,7 +2599,6 @@
         <f>B106+C106</f>
         <v/>
       </c>
-      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2700,7 +2616,6 @@
         <f>B107+C107</f>
         <v/>
       </c>
-      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
@@ -2718,7 +2633,6 @@
         <f>B108+C108</f>
         <v/>
       </c>
-      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2736,7 +2650,6 @@
         <f>B109+C109</f>
         <v/>
       </c>
-      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2754,7 +2667,6 @@
         <f>B110+C110</f>
         <v/>
       </c>
-      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2772,7 +2684,6 @@
         <f>B111+C111</f>
         <v/>
       </c>
-      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2812,7 +2723,6 @@
         <f>B113+C113</f>
         <v/>
       </c>
-      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2830,7 +2740,6 @@
         <f>B114+C114</f>
         <v/>
       </c>
-      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2870,7 +2779,6 @@
         <f>B116+C116</f>
         <v/>
       </c>
-      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2888,7 +2796,6 @@
         <f>B117+C117</f>
         <v/>
       </c>
-      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2906,7 +2813,6 @@
         <f>B118+C118</f>
         <v/>
       </c>
-      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
@@ -2924,7 +2830,6 @@
         <f>B119+C119</f>
         <v/>
       </c>
-      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2942,7 +2847,6 @@
         <f>B120+C120</f>
         <v/>
       </c>
-      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2960,7 +2864,6 @@
         <f>B121+C121</f>
         <v/>
       </c>
-      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3000,7 +2903,6 @@
         <f>B123+C123</f>
         <v/>
       </c>
-      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
@@ -3018,7 +2920,6 @@
         <f>B124+C124</f>
         <v/>
       </c>
-      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3036,7 +2937,6 @@
         <f>B125+C125</f>
         <v/>
       </c>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3054,7 +2954,6 @@
         <f>B126+C126</f>
         <v/>
       </c>
-      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
@@ -3072,7 +2971,6 @@
         <f>B127+C127</f>
         <v/>
       </c>
-      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3090,7 +2988,6 @@
         <f>B128+C128</f>
         <v/>
       </c>
-      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="19" t="inlineStr">
@@ -3108,7 +3005,6 @@
         <f>B129+C129</f>
         <v/>
       </c>
-      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3126,7 +3022,6 @@
         <f>B130+C130</f>
         <v/>
       </c>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3144,7 +3039,6 @@
         <f>B131+C131</f>
         <v/>
       </c>
-      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3162,7 +3056,6 @@
         <f>B132+C132</f>
         <v/>
       </c>
-      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3180,7 +3073,6 @@
         <f>B133+C133</f>
         <v/>
       </c>
-      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3308,7 +3200,6 @@
         <f>B139+C139</f>
         <v/>
       </c>
-      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3370,7 +3261,6 @@
         <f>B142+C142</f>
         <v/>
       </c>
-      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3388,7 +3278,6 @@
         <f>B143+C143</f>
         <v/>
       </c>
-      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3406,7 +3295,6 @@
         <f>B144+C144</f>
         <v/>
       </c>
-      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3424,7 +3312,6 @@
         <f>B145+C145</f>
         <v/>
       </c>
-      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3464,7 +3351,6 @@
         <f>B147+C147</f>
         <v/>
       </c>
-      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3482,7 +3368,6 @@
         <f>B148+C148</f>
         <v/>
       </c>
-      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3500,7 +3385,6 @@
         <f>B149+C149</f>
         <v/>
       </c>
-      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3518,7 +3402,6 @@
         <f>B150+C150</f>
         <v/>
       </c>
-      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3580,7 +3463,6 @@
         <f>B153+C153</f>
         <v/>
       </c>
-      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3620,7 +3502,6 @@
         <f>B155+C155</f>
         <v/>
       </c>
-      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3638,7 +3519,6 @@
         <f>B156+C156</f>
         <v/>
       </c>
-      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3656,7 +3536,6 @@
         <f>B157+C157</f>
         <v/>
       </c>
-      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3674,7 +3553,6 @@
         <f>B158+C158</f>
         <v/>
       </c>
-      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3714,7 +3592,6 @@
         <f>B160+C160</f>
         <v/>
       </c>
-      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3732,7 +3609,6 @@
         <f>B161+C161</f>
         <v/>
       </c>
-      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -3772,7 +3648,6 @@
         <f>B163+C163</f>
         <v/>
       </c>
-      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="19" t="inlineStr">
@@ -3790,7 +3665,6 @@
         <f>B164+C164</f>
         <v/>
       </c>
-      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
@@ -3808,7 +3682,6 @@
         <f>B165+C165</f>
         <v/>
       </c>
-      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -3826,7 +3699,6 @@
         <f>B166+C166</f>
         <v/>
       </c>
-      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -3844,7 +3716,6 @@
         <f>B167+C167</f>
         <v/>
       </c>
-      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -3862,7 +3733,6 @@
         <f>B168+C168</f>
         <v/>
       </c>
-      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -3880,7 +3750,6 @@
         <f>B169+C169</f>
         <v/>
       </c>
-      <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -3898,7 +3767,6 @@
         <f>B170+C170</f>
         <v/>
       </c>
-      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -3960,7 +3828,6 @@
         <f>B173+C173</f>
         <v/>
       </c>
-      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4000,7 +3867,6 @@
         <f>B175+C175</f>
         <v/>
       </c>
-      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4018,7 +3884,6 @@
         <f>B176+C176</f>
         <v/>
       </c>
-      <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4036,7 +3901,6 @@
         <f>B177+C177</f>
         <v/>
       </c>
-      <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4054,7 +3918,6 @@
         <f>B178+C178</f>
         <v/>
       </c>
-      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4072,7 +3935,6 @@
         <f>B179+C179</f>
         <v/>
       </c>
-      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4134,7 +3996,6 @@
         <f>B182+C182</f>
         <v/>
       </c>
-      <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -4152,7 +4013,6 @@
         <f>B183+C183</f>
         <v/>
       </c>
-      <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
@@ -4170,7 +4030,6 @@
         <f>B184+C184</f>
         <v/>
       </c>
-      <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -4188,7 +4047,6 @@
         <f>B185+C185</f>
         <v/>
       </c>
-      <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -4206,7 +4064,6 @@
         <f>B186+C186</f>
         <v/>
       </c>
-      <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -4224,7 +4081,6 @@
         <f>B187+C187</f>
         <v/>
       </c>
-      <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -4242,7 +4098,6 @@
         <f>B188+C188</f>
         <v/>
       </c>
-      <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -4260,7 +4115,6 @@
         <f>B189+C189</f>
         <v/>
       </c>
-      <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -4300,7 +4154,6 @@
         <f>B191+C191</f>
         <v/>
       </c>
-      <c r="E191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -4445,7 +4298,6 @@
         <f>B198+C198</f>
         <v/>
       </c>
-      <c r="E198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -4463,7 +4315,6 @@
         <f>B199+C199</f>
         <v/>
       </c>
-      <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -4481,7 +4332,6 @@
         <f>B200+C200</f>
         <v/>
       </c>
-      <c r="E200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -4499,7 +4349,6 @@
         <f>B201+C201</f>
         <v/>
       </c>
-      <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -4517,7 +4366,6 @@
         <f>B202+C202</f>
         <v/>
       </c>
-      <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -4535,7 +4383,6 @@
         <f>B203+C203</f>
         <v/>
       </c>
-      <c r="E203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -4575,7 +4422,6 @@
         <f>B205+C205</f>
         <v/>
       </c>
-      <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -4593,7 +4439,6 @@
         <f>B206+C206</f>
         <v/>
       </c>
-      <c r="E206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -4655,7 +4500,6 @@
         <f>B209+C209</f>
         <v/>
       </c>
-      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -4673,7 +4517,6 @@
         <f>B210+C210</f>
         <v/>
       </c>
-      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -4691,7 +4534,6 @@
         <f>B211+C211</f>
         <v/>
       </c>
-      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -4709,7 +4551,6 @@
         <f>B212+C212</f>
         <v/>
       </c>
-      <c r="E212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -4771,7 +4612,6 @@
         <f>B215+C215</f>
         <v/>
       </c>
-      <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -4811,7 +4651,6 @@
         <f>B217+C217</f>
         <v/>
       </c>
-      <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -4829,7 +4668,6 @@
         <f>B218+C218</f>
         <v/>
       </c>
-      <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -4847,7 +4685,6 @@
         <f>B219+C219</f>
         <v/>
       </c>
-      <c r="E219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -4997,7 +4834,6 @@
         <f>B226+C226</f>
         <v/>
       </c>
-      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -5015,7 +4851,6 @@
         <f>B227+C227</f>
         <v/>
       </c>
-      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -5033,7 +4868,6 @@
         <f>B228+C228</f>
         <v/>
       </c>
-      <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -5051,7 +4885,6 @@
         <f>B229+C229</f>
         <v/>
       </c>
-      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -5201,7 +5034,6 @@
         <f>B236+C236</f>
         <v/>
       </c>
-      <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -5219,7 +5051,6 @@
         <f>B237+C237</f>
         <v/>
       </c>
-      <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -5281,7 +5112,6 @@
         <f>B240+C240</f>
         <v/>
       </c>
-      <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
@@ -5299,7 +5129,6 @@
         <f>B241+C241</f>
         <v/>
       </c>
-      <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
@@ -5317,7 +5146,6 @@
         <f>B242+C242</f>
         <v/>
       </c>
-      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
@@ -5357,7 +5185,6 @@
         <f>B244+C244</f>
         <v/>
       </c>
-      <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
@@ -5397,7 +5224,6 @@
         <f>B246+C246</f>
         <v/>
       </c>
-      <c r="E246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -5415,7 +5241,6 @@
         <f>B247+C247</f>
         <v/>
       </c>
-      <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -5433,7 +5258,6 @@
         <f>B248+C248</f>
         <v/>
       </c>
-      <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
@@ -5451,7 +5275,6 @@
         <f>B249+C249</f>
         <v/>
       </c>
-      <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
@@ -5530,7 +5353,6 @@
         <f>B253+C253</f>
         <v/>
       </c>
-      <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -5548,7 +5370,6 @@
         <f>B254+C254</f>
         <v/>
       </c>
-      <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -5566,7 +5387,6 @@
         <f>B255+C255</f>
         <v/>
       </c>
-      <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="17" t="inlineStr">
@@ -5584,7 +5404,6 @@
         <f>B256+C256</f>
         <v/>
       </c>
-      <c r="E256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="17" t="inlineStr">
@@ -5602,7 +5421,6 @@
         <f>B257+C257</f>
         <v/>
       </c>
-      <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
@@ -5620,7 +5438,6 @@
         <f>B258+C258</f>
         <v/>
       </c>
-      <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="17" t="inlineStr">
@@ -5638,7 +5455,6 @@
         <f>B259+C259</f>
         <v/>
       </c>
-      <c r="E259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="17" t="inlineStr">
@@ -5656,7 +5472,6 @@
         <f>B260+C260</f>
         <v/>
       </c>
-      <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -5674,7 +5489,6 @@
         <f>B261+C261</f>
         <v/>
       </c>
-      <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -5692,7 +5506,6 @@
         <f>B262+C262</f>
         <v/>
       </c>
-      <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="17" t="inlineStr">
@@ -5710,7 +5523,6 @@
         <f>B263+C263</f>
         <v/>
       </c>
-      <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="17" t="inlineStr">
@@ -5728,7 +5540,6 @@
         <f>B264+C264</f>
         <v/>
       </c>
-      <c r="E264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="17" t="inlineStr">
@@ -5746,7 +5557,6 @@
         <f>B265+C265</f>
         <v/>
       </c>
-      <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
@@ -5764,7 +5574,6 @@
         <f>B266+C266</f>
         <v/>
       </c>
-      <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="17" t="inlineStr">
@@ -5804,7 +5613,6 @@
         <f>B268+C268</f>
         <v/>
       </c>
-      <c r="E268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5822,7 +5630,6 @@
         <f>B269+C269</f>
         <v/>
       </c>
-      <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5840,7 +5647,6 @@
         <f>B270+C270</f>
         <v/>
       </c>
-      <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5868,7 +5674,6 @@
         <f>B272+C272</f>
         <v/>
       </c>
-      <c r="E272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5908,7 +5713,6 @@
         <f>B274+C274</f>
         <v/>
       </c>
-      <c r="E274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5926,7 +5730,6 @@
         <f>B275+C275</f>
         <v/>
       </c>
-      <c r="E275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5944,7 +5747,6 @@
         <f>B276+C276</f>
         <v/>
       </c>
-      <c r="E276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5984,7 +5786,6 @@
         <f>B278+C278</f>
         <v/>
       </c>
-      <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6002,7 +5803,6 @@
         <f>B279+C279</f>
         <v/>
       </c>
-      <c r="E279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6030,7 +5830,6 @@
         <f>B281+C281</f>
         <v/>
       </c>
-      <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6048,7 +5847,6 @@
         <f>B282+C282</f>
         <v/>
       </c>
-      <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6066,7 +5864,6 @@
         <f>B283+C283</f>
         <v/>
       </c>
-      <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6084,7 +5881,6 @@
         <f>B284+C284</f>
         <v/>
       </c>
-      <c r="E284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6102,7 +5898,6 @@
         <f>B285+C285</f>
         <v/>
       </c>
-      <c r="E285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6266,7 +6061,6 @@
         <f>B297+C297</f>
         <v/>
       </c>
-      <c r="E297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6370,7 +6164,6 @@
         <f>B303+C303</f>
         <v/>
       </c>
-      <c r="E303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -32086,7 +31879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C708"/>
+  <dimension ref="A1:D708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.109375" customWidth="1" style="40" min="1" max="1"/>
@@ -32107,6 +31900,11 @@
       <c r="C1" s="38" t="inlineStr">
         <is>
           <t>Süre</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Büküm Op.</t>
         </is>
       </c>
     </row>
